--- a/r4-core-add-vbpk/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-add-vbpk/StructureDefinition-at-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3064" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3461" uniqueCount="497">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T11:03:52+00:00</t>
+    <t>2026-06-12T11:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -924,50 +924,264 @@
     <t>Practitioner.identifier:vbPK.type</t>
   </si>
   <si>
-    <t>Practitioner.identifier:vbPK.system</t>
-  </si>
-  <si>
-    <t>OID for the vbPK in Austria</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.40.0.34.4.22</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.value</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.period</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.id</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.reference</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.type</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.display</t>
-  </si>
-  <si>
-    <t>Bundesministerium für Inneres</t>
-  </si>
-  <si>
-    <t>Practitioner.active</t>
+    <t>Practitioner.identifier:vbPK.type.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier.type.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:vbPK.type.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier.type.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:vbPK.type.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:vbPK.type.coding.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier.type.coding.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:vbPK.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:vbPK.type.coding.system</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier.type.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:vbPK.type.coding.version</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier.type.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:vbPK.type.coding.code</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier.type.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>NI</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:vbPK.type.coding.display</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier.type.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:vbPK.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier.type.coding.userSelected</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
 </t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:vbPK.type.text</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier.type.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:vbPK.system</t>
+  </si>
+  <si>
+    <t>OID for the vbPK in Austria</t>
+  </si>
+  <si>
+    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/ValueSet/at-core-valueset-vbpk</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:vbPK.value</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:vbPK.period</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:vbPK.assigner</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:vbPK.assigner.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:vbPK.assigner.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:vbPK.assigner.reference</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:vbPK.assigner.type</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:vbPK.assigner.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:vbPK.assigner.display</t>
+  </si>
+  <si>
+    <t>Bundesministerium für Inneres</t>
+  </si>
+  <si>
+    <t>Practitioner.active</t>
   </si>
   <si>
     <t>Whether this practitioner's record is in active use</t>
@@ -1648,11 +1862,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN84"/>
+  <dimension ref="A1:AN95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.5625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="34.8984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.05078125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="24.671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1676,7 +1890,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="51.97265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="46.58203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.3046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -1686,7 +1900,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.65625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="39.109375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="87.9765625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="44.90625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
@@ -7300,7 +7514,7 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
@@ -7805,7 +8019,7 @@
         <v>21</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
@@ -7859,7 +8073,7 @@
         <v>294</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>187</v>
+        <v>295</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7867,7 +8081,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>88</v>
@@ -7879,35 +8093,31 @@
         <v>21</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>102</v>
+        <v>157</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>295</v>
+        <v>158</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>191</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>296</v>
+        <v>21</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>21</v>
@@ -7943,7 +8153,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>193</v>
+        <v>160</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7955,16 +8165,16 @@
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>194</v>
+        <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>195</v>
+        <v>161</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>196</v>
+        <v>21</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
@@ -7972,21 +8182,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B56" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>21</v>
@@ -7995,19 +8205,19 @@
         <v>21</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>198</v>
+        <v>135</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>200</v>
+        <v>137</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8021,7 +8231,7 @@
         <v>21</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>21</v>
@@ -8045,40 +8255,40 @@
         <v>21</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>21</v>
+        <v>164</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8089,7 +8299,7 @@
         <v>298</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>206</v>
+        <v>299</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8100,7 +8310,7 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
@@ -8112,16 +8322,20 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>207</v>
+        <v>300</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>208</v>
+        <v>301</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8169,13 +8383,13 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>210</v>
+        <v>305</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
@@ -8184,13 +8398,13 @@
         <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>211</v>
+        <v>306</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>212</v>
+        <v>307</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8198,10 +8412,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>214</v>
+        <v>309</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8221,20 +8435,18 @@
         <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>215</v>
+        <v>157</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>216</v>
+        <v>158</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -8283,7 +8495,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>219</v>
+        <v>160</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8295,16 +8507,16 @@
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>220</v>
+        <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>221</v>
+        <v>161</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
@@ -8312,21 +8524,21 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>237</v>
+        <v>311</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
@@ -8338,15 +8550,17 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -8383,31 +8597,31 @@
         <v>21</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>21</v>
+        <v>164</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
@@ -8424,21 +8638,21 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>239</v>
+        <v>313</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>21</v>
@@ -8447,27 +8661,29 @@
         <v>21</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>135</v>
+        <v>314</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>163</v>
+        <v>315</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>21</v>
+        <v>318</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>21</v>
@@ -8497,37 +8713,37 @@
         <v>21</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>166</v>
+        <v>319</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>161</v>
+        <v>321</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>21</v>
@@ -8538,10 +8754,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>241</v>
+        <v>323</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8567,13 +8783,13 @@
         <v>157</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>242</v>
+        <v>324</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>243</v>
+        <v>325</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>244</v>
+        <v>326</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8623,7 +8839,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>245</v>
+        <v>327</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8632,16 +8848,16 @@
         <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>131</v>
+        <v>329</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>21</v>
@@ -8652,10 +8868,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>303</v>
+        <v>330</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>248</v>
+        <v>331</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8678,24 +8894,24 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>249</v>
+        <v>332</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>21</v>
+        <v>335</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>21</v>
@@ -8713,13 +8929,13 @@
         <v>21</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>252</v>
+        <v>21</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>253</v>
+        <v>21</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>21</v>
@@ -8737,7 +8953,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>254</v>
+        <v>336</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8752,10 +8968,10 @@
         <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>21</v>
+        <v>337</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>131</v>
+        <v>338</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>21</v>
@@ -8766,10 +8982,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>304</v>
+        <v>339</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>256</v>
+        <v>340</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8792,18 +9008,18 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>257</v>
+        <v>341</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -8851,7 +9067,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>260</v>
+        <v>344</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8866,10 +9082,10 @@
         <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>21</v>
+        <v>345</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>261</v>
+        <v>346</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>21</v>
@@ -8880,10 +9096,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>305</v>
+        <v>347</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>263</v>
+        <v>348</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8906,24 +9122,26 @@
         <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>157</v>
+        <v>349</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>264</v>
+        <v>350</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>265</v>
+        <v>351</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>306</v>
+        <v>21</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>21</v>
@@ -8965,7 +9183,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>268</v>
+        <v>354</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8980,10 +9198,10 @@
         <v>100</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>21</v>
+        <v>355</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>131</v>
+        <v>356</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>21</v>
@@ -8994,10 +9212,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>307</v>
+        <v>357</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>307</v>
+        <v>358</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9020,26 +9238,24 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>308</v>
+        <v>157</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>309</v>
+        <v>359</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>311</v>
+        <v>361</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>312</v>
+        <v>362</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q65" t="s" s="2">
-        <v>313</v>
-      </c>
+      <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9083,7 +9299,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>307</v>
+        <v>363</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9098,24 +9314,24 @@
         <v>100</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>21</v>
+        <v>364</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>314</v>
+        <v>365</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>315</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>316</v>
+        <v>366</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>316</v>
+        <v>187</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9123,10 +9339,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>21</v>
@@ -9138,19 +9354,19 @@
         <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>317</v>
+        <v>102</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>318</v>
+        <v>367</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>319</v>
+        <v>189</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>320</v>
+        <v>190</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>321</v>
+        <v>191</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -9163,7 +9379,7 @@
         <v>21</v>
       </c>
       <c r="T66" t="s" s="2">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="U66" t="s" s="2">
         <v>21</v>
@@ -9175,13 +9391,11 @@
         <v>21</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>21</v>
+        <v>368</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
@@ -9199,13 +9413,13 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>316</v>
+        <v>193</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>21</v>
@@ -9214,13 +9428,13 @@
         <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>322</v>
+        <v>194</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>324</v>
+        <v>196</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -9228,10 +9442,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>325</v>
+        <v>369</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>325</v>
+        <v>197</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9239,10 +9453,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>21</v>
@@ -9254,20 +9468,18 @@
         <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>326</v>
+        <v>157</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>327</v>
+        <v>198</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>328</v>
+        <v>199</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
@@ -9279,7 +9491,7 @@
         <v>21</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>21</v>
@@ -9315,13 +9527,13 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>325</v>
+        <v>202</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
@@ -9330,13 +9542,13 @@
         <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>331</v>
+        <v>203</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>332</v>
+        <v>204</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>333</v>
+        <v>205</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -9344,10 +9556,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>334</v>
+        <v>370</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>334</v>
+        <v>206</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9358,7 +9570,7 @@
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>21</v>
@@ -9370,20 +9582,16 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>335</v>
+        <v>207</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>336</v>
+        <v>208</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>339</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>21</v>
       </c>
@@ -9431,13 +9639,13 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>334</v>
+        <v>210</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
@@ -9446,13 +9654,13 @@
         <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>340</v>
+        <v>211</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>341</v>
+        <v>212</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>342</v>
+        <v>213</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -9460,10 +9668,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>343</v>
+        <v>371</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>343</v>
+        <v>214</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9486,18 +9694,18 @@
         <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>108</v>
+        <v>215</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>344</v>
+        <v>216</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" t="s" s="2">
-        <v>346</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>21</v>
       </c>
@@ -9521,13 +9729,13 @@
         <v>21</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>347</v>
+        <v>21</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>348</v>
+        <v>21</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>21</v>
@@ -9545,7 +9753,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>343</v>
+        <v>219</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9560,13 +9768,13 @@
         <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>349</v>
+        <v>220</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>350</v>
+        <v>221</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>351</v>
+        <v>222</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -9574,10 +9782,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>352</v>
+        <v>237</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9603,10 +9811,10 @@
         <v>157</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>353</v>
+        <v>158</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>354</v>
+        <v>159</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9675,7 +9883,7 @@
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>21</v>
@@ -9686,14 +9894,14 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>355</v>
+        <v>239</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -9715,12 +9923,14 @@
         <v>134</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>356</v>
+        <v>135</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>21</v>
@@ -9759,7 +9969,9 @@
       <c r="AB71" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="AC71" s="2"/>
+      <c r="AC71" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="AD71" t="s" s="2">
         <v>21</v>
       </c>
@@ -9785,7 +9997,7 @@
         <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>21</v>
@@ -9796,14 +10008,12 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="C72" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>21</v>
       </c>
@@ -9821,18 +10031,20 @@
         <v>21</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>360</v>
+        <v>157</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>361</v>
+        <v>242</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>21</v>
@@ -9881,25 +10093,25 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>166</v>
+        <v>245</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>363</v>
+        <v>246</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>21</v>
@@ -9910,10 +10122,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>364</v>
+        <v>248</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9933,18 +10145,20 @@
         <v>21</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>365</v>
+        <v>249</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -9969,13 +10183,13 @@
         <v>21</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>21</v>
+        <v>252</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>21</v>
+        <v>253</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>21</v>
@@ -9993,7 +10207,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>366</v>
+        <v>254</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10005,13 +10219,13 @@
         <v>21</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>21</v>
@@ -10022,10 +10236,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>367</v>
+        <v>256</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10048,18 +10262,18 @@
         <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>368</v>
+        <v>146</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>369</v>
+        <v>257</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" t="s" s="2">
-        <v>371</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>21</v>
       </c>
@@ -10107,7 +10321,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>367</v>
+        <v>260</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10122,13 +10336,13 @@
         <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>372</v>
+        <v>21</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>373</v>
+        <v>261</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>374</v>
+        <v>21</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -10136,10 +10350,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>375</v>
+        <v>263</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10150,7 +10364,7 @@
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>21</v>
@@ -10159,27 +10373,27 @@
         <v>21</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>376</v>
+        <v>157</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>377</v>
+        <v>264</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>21</v>
+        <v>378</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>21</v>
@@ -10221,13 +10435,13 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>375</v>
+        <v>268</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>21</v>
@@ -10239,10 +10453,10 @@
         <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>380</v>
+        <v>131</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>381</v>
+        <v>21</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
@@ -10250,10 +10464,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10264,7 +10478,7 @@
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>21</v>
@@ -10273,23 +10487,29 @@
         <v>21</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="O76" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="P76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q76" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M76" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
         <v>21</v>
       </c>
@@ -10333,13 +10553,13 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>21</v>
@@ -10348,24 +10568,24 @@
         <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10376,7 +10596,7 @@
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>21</v>
@@ -10385,19 +10605,23 @@
         <v>21</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>157</v>
+        <v>388</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>158</v>
+        <v>389</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>21</v>
       </c>
@@ -10445,28 +10669,28 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>160</v>
+        <v>387</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>21</v>
+        <v>393</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>161</v>
+        <v>394</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>21</v>
+        <v>395</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>21</v>
@@ -10474,14 +10698,14 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -10497,21 +10721,23 @@
         <v>21</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>134</v>
+        <v>397</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>135</v>
+        <v>398</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>163</v>
+        <v>399</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
       </c>
@@ -10559,7 +10785,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>166</v>
+        <v>396</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10571,16 +10797,16 @@
         <v>21</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>21</v>
+        <v>402</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>161</v>
+        <v>403</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>21</v>
+        <v>404</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
@@ -10588,14 +10814,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>392</v>
+        <v>21</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -10608,25 +10834,25 @@
         <v>21</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J79" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>134</v>
+        <v>406</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>137</v>
+        <v>409</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>143</v>
+        <v>410</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>21</v>
@@ -10675,7 +10901,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10687,16 +10913,16 @@
         <v>21</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>21</v>
+        <v>411</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>131</v>
+        <v>412</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>21</v>
+        <v>413</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>21</v>
@@ -10704,10 +10930,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10718,7 +10944,7 @@
         <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>21</v>
@@ -10727,20 +10953,20 @@
         <v>21</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>21</v>
@@ -10765,13 +10991,13 @@
         <v>21</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>21</v>
+        <v>419</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>21</v>
@@ -10789,13 +11015,13 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>21</v>
@@ -10804,13 +11030,13 @@
         <v>100</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>21</v>
+        <v>420</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>21</v>
+        <v>422</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>21</v>
@@ -10818,10 +11044,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>401</v>
+        <v>423</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>401</v>
+        <v>423</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10829,7 +11055,7 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>88</v>
@@ -10844,13 +11070,13 @@
         <v>21</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10877,13 +11103,13 @@
         <v>21</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>404</v>
+        <v>21</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>405</v>
+        <v>21</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>406</v>
+        <v>21</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>21</v>
@@ -10901,10 +11127,10 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>401</v>
+        <v>160</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>88</v>
@@ -10913,16 +11139,16 @@
         <v>21</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>387</v>
+        <v>21</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>407</v>
+        <v>21</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
@@ -10930,10 +11156,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10944,7 +11170,7 @@
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>21</v>
@@ -10956,18 +11182,16 @@
         <v>21</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>207</v>
+        <v>134</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="N82" s="2"/>
-      <c r="O82" t="s" s="2">
-        <v>411</v>
-      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>21</v>
       </c>
@@ -11003,40 +11227,38 @@
         <v>21</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="AC82" s="2"/>
       <c r="AD82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>408</v>
+        <v>166</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>412</v>
+        <v>21</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>413</v>
+        <v>21</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>21</v>
@@ -11044,12 +11266,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="C83" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="D83" t="s" s="2">
         <v>21</v>
       </c>
@@ -11070,13 +11294,13 @@
         <v>21</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>215</v>
+        <v>431</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11127,25 +11351,25 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>414</v>
+        <v>166</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>21</v>
+        <v>434</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>417</v>
+        <v>21</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>21</v>
@@ -11156,10 +11380,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11170,7 +11394,7 @@
         <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>21</v>
@@ -11182,20 +11406,16 @@
         <v>21</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>419</v>
+        <v>436</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>21</v>
       </c>
@@ -11219,54 +11439,1304 @@
         <v>21</v>
       </c>
       <c r="X84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="P86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="P90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="P95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X95" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="Y84" t="s" s="2">
+      <c r="Y95" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="Z84" t="s" s="2">
+      <c r="Z95" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="AA84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH84" t="s" s="2">
+      <c r="AA95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH95" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AI84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
+      <c r="AI95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AK84" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AN84" t="s" s="2">
+      <c r="AK95" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>21</v>
       </c>
     </row>
